--- a/src/test/fixtures/forms-responses-http/multi-export-es.xlsx
+++ b/src/test/fixtures/forms-responses-http/multi-export-es.xlsx
@@ -36,7 +36,7 @@
     <x:t>Riesgos históricos</x:t>
   </x:si>
   <x:si>
-    <x:t>T14693031-000001</x:t>
+    <x:t>TF931104E-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -48,7 +48,7 @@
     <x:t>Ruido histórico; Frío histórico</x:t>
   </x:si>
   <x:si>
-    <x:t>T14693031-000002</x:t>
+    <x:t>TF931104E-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Frío</x:t>
@@ -57,10 +57,10 @@
     <x:t>Frío histórico</x:t>
   </x:si>
   <x:si>
-    <x:t>T14693031-000003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T14693031-000004</x:t>
+    <x:t>TF931104E-000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TF931104E-000004</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/multi-export-es.xlsx
+++ b/src/test/fixtures/forms-responses-http/multi-export-es.xlsx
@@ -36,7 +36,7 @@
     <x:t>Riesgos históricos</x:t>
   </x:si>
   <x:si>
-    <x:t>TF931104E-000001</x:t>
+    <x:t>T7F3A201E-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -48,7 +48,7 @@
     <x:t>Ruido histórico; Frío histórico</x:t>
   </x:si>
   <x:si>
-    <x:t>TF931104E-000002</x:t>
+    <x:t>T7F3A201E-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Frío</x:t>
@@ -57,10 +57,10 @@
     <x:t>Frío histórico</x:t>
   </x:si>
   <x:si>
-    <x:t>TF931104E-000003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TF931104E-000004</x:t>
+    <x:t>T7F3A201E-000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T7F3A201E-000004</x:t>
   </x:si>
 </x:sst>
 </file>

--- a/src/test/fixtures/forms-responses-http/multi-export-es.xlsx
+++ b/src/test/fixtures/forms-responses-http/multi-export-es.xlsx
@@ -36,7 +36,7 @@
     <x:t>Riesgos históricos</x:t>
   </x:si>
   <x:si>
-    <x:t>T7F3A201E-000001</x:t>
+    <x:t>T9ECA8C57-000001</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
@@ -48,7 +48,7 @@
     <x:t>Ruido histórico; Frío histórico</x:t>
   </x:si>
   <x:si>
-    <x:t>T7F3A201E-000002</x:t>
+    <x:t>T9ECA8C57-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Frío</x:t>
@@ -57,10 +57,10 @@
     <x:t>Frío histórico</x:t>
   </x:si>
   <x:si>
-    <x:t>T7F3A201E-000003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T7F3A201E-000004</x:t>
+    <x:t>T9ECA8C57-000003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T9ECA8C57-000004</x:t>
   </x:si>
 </x:sst>
 </file>
